--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CDFFC52-4780-48FE-B7FA-224A4DAD508E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF6C2F0-FBDB-472F-B538-1574B6A91175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="9" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
-    <sheet name="SalesRep" sheetId="2" r:id="rId2"/>
-    <sheet name="InsideSalesRep" sheetId="8" r:id="rId3"/>
-    <sheet name="CSR" sheetId="9" r:id="rId4"/>
-    <sheet name="Customers" sheetId="3" r:id="rId5"/>
-    <sheet name="Generators" sheetId="6" r:id="rId6"/>
-    <sheet name="TankNumber" sheetId="4" r:id="rId7"/>
+    <sheet name="Invoices" sheetId="11" r:id="rId2"/>
+    <sheet name="SalesRep" sheetId="2" r:id="rId3"/>
+    <sheet name="InsideSalesRep" sheetId="8" r:id="rId4"/>
+    <sheet name="CSR" sheetId="9" r:id="rId5"/>
+    <sheet name="Customers" sheetId="3" r:id="rId6"/>
+    <sheet name="Generators" sheetId="6" r:id="rId7"/>
     <sheet name="Facilities" sheetId="5" r:id="rId8"/>
-    <sheet name="ManifestProfiles" sheetId="7" r:id="rId9"/>
-    <sheet name="Container" sheetId="10" r:id="rId10"/>
+    <sheet name="TankNumber" sheetId="4" r:id="rId9"/>
+    <sheet name="ManifestProfiles" sheetId="7" r:id="rId10"/>
+    <sheet name="Container" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
   <si>
     <t>UserName</t>
   </si>
@@ -369,6 +370,33 @@
   </si>
   <si>
     <t>M</t>
+  </si>
+  <si>
+    <t>Morgantown</t>
+  </si>
+  <si>
+    <t>InvoiceID</t>
+  </si>
+  <si>
+    <t>559096,561190</t>
+  </si>
+  <si>
+    <t>557108,551630,555000</t>
+  </si>
+  <si>
+    <t>565495,563053,562094,555793</t>
+  </si>
+  <si>
+    <t>Document Types</t>
+  </si>
+  <si>
+    <t>BOL,CD,LDR,Manifest and Ticket Bundle</t>
+  </si>
+  <si>
+    <t>Manifest-Final,Manifest-Initial,Packing Slip</t>
+  </si>
+  <si>
+    <t>Photo,Weight Ticket</t>
   </si>
 </sst>
 </file>
@@ -410,10 +438,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1017,6 +1046,68 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67A0C787-9629-4F1D-ABA0-794DC4D85B37}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="63.90625" customWidth="1"/>
+    <col min="2" max="2" width="44.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1864127C-45A9-4213-9B60-F5C546F8339D}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1107,6 +1198,52 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C34AAF-0049-4621-ACC0-F8AB61C4FEAD}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.26953125" customWidth="1"/>
+    <col min="2" max="2" width="35.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CC3F5A7-8070-4DB3-B4FB-5D24721A9DCF}">
   <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1274,7 +1411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0388301D-1ED3-4DEE-88AA-4F5341C838EB}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1317,7 +1454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B27D0A0C-EDD4-41D7-A808-64E38BFF62E9}">
   <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1380,7 +1517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8441AC03-8AA1-4A52-B022-D9D96F5EE941}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1423,9 +1560,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91236A0F-D4E4-4590-95E3-BE447AD5E61E}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" customWidth="1"/>
@@ -1451,122 +1588,9 @@
         <v>689720</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED234D9-31DD-472B-A027-353CCE1DF9EB}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="11.08984375" customWidth="1"/>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="18.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>213</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2">
-        <v>87056</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>214</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3">
-        <v>87057</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>215</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>87058</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>216</v>
-      </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>217</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>218</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>222</v>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1623,60 +1647,116 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67A0C787-9629-4F1D-ABA0-794DC4D85B37}">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED234D9-31DD-472B-A027-353CCE1DF9EB}">
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="63.90625" customWidth="1"/>
-    <col min="2" max="2" width="44.36328125" customWidth="1"/>
+    <col min="1" max="1" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>65</v>
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>213</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>67</v>
+        <v>43</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2">
+        <v>87056</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>214</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>69</v>
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3">
+        <v>87057</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>215</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>71</v>
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>87058</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>216</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>217</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>218</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF6C2F0-FBDB-472F-B538-1574B6A91175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCA75C8-D14E-438D-8BA1-C1CE920F777B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="11" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="TankNumber" sheetId="4" r:id="rId9"/>
     <sheet name="ManifestProfiles" sheetId="7" r:id="rId10"/>
     <sheet name="Container" sheetId="10" r:id="rId11"/>
+    <sheet name="Values" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
   <si>
     <t>UserName</t>
   </si>
@@ -397,6 +398,48 @@
   </si>
   <si>
     <t>Photo,Weight Ticket</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Inactive/Cancelled</t>
+  </si>
+  <si>
+    <t>Pending/New</t>
+  </si>
+  <si>
+    <t>Inactive/Expired</t>
+  </si>
+  <si>
+    <t>Pending/Submitted</t>
+  </si>
+  <si>
+    <t>Inactive/Archived</t>
+  </si>
+  <si>
+    <t>Active/Approved</t>
+  </si>
+  <si>
+    <t>Pending/Ready for Generator Signature</t>
+  </si>
+  <si>
+    <t>Inactive/Incineration Prep</t>
+  </si>
+  <si>
+    <t>Pending/Recertify</t>
+  </si>
+  <si>
+    <t>Pending/Web Recert</t>
+  </si>
+  <si>
+    <t>Pending/Signature Received</t>
+  </si>
+  <si>
+    <t>Pending/Resubmit</t>
+  </si>
+  <si>
+    <t>Pending/Sent for Generator Signature</t>
   </si>
 </sst>
 </file>
@@ -777,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAD53460-8519-44AA-AE90-EBABC7390FF4}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.36328125" customWidth="1"/>
@@ -1038,6 +1081,1854 @@
       </c>
       <c r="D28" s="1">
         <v>45902</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C29" s="1">
+        <v>45836</v>
+      </c>
+      <c r="D29" s="1">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C30" s="1">
+        <v>45837</v>
+      </c>
+      <c r="D30" s="1">
+        <v>45904</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C31" s="1">
+        <v>45838</v>
+      </c>
+      <c r="D31" s="1">
+        <v>45905</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C32" s="1">
+        <v>45839</v>
+      </c>
+      <c r="D32" s="1">
+        <v>45906</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C33" s="1">
+        <v>45840</v>
+      </c>
+      <c r="D33" s="1">
+        <v>45907</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C34" s="1">
+        <v>45841</v>
+      </c>
+      <c r="D34" s="1">
+        <v>45908</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C35" s="1">
+        <v>45842</v>
+      </c>
+      <c r="D35" s="1">
+        <v>45909</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C36" s="1">
+        <v>45843</v>
+      </c>
+      <c r="D36" s="1">
+        <v>45910</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C37" s="1">
+        <v>45844</v>
+      </c>
+      <c r="D37" s="1">
+        <v>45911</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C38" s="1">
+        <v>45845</v>
+      </c>
+      <c r="D38" s="1">
+        <v>45912</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C39" s="1">
+        <v>45846</v>
+      </c>
+      <c r="D39" s="1">
+        <v>45913</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C40" s="1">
+        <v>45847</v>
+      </c>
+      <c r="D40" s="1">
+        <v>45914</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C41" s="1">
+        <v>45848</v>
+      </c>
+      <c r="D41" s="1">
+        <v>45915</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C42" s="1">
+        <v>45849</v>
+      </c>
+      <c r="D42" s="1">
+        <v>45916</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C43" s="1">
+        <v>45850</v>
+      </c>
+      <c r="D43" s="1">
+        <v>45917</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C44" s="1">
+        <v>45851</v>
+      </c>
+      <c r="D44" s="1">
+        <v>45918</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C45" s="1">
+        <v>45852</v>
+      </c>
+      <c r="D45" s="1">
+        <v>45919</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C46" s="1">
+        <v>45853</v>
+      </c>
+      <c r="D46" s="1">
+        <v>45920</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C47" s="1">
+        <v>45854</v>
+      </c>
+      <c r="D47" s="1">
+        <v>45921</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C48" s="1">
+        <v>45855</v>
+      </c>
+      <c r="D48" s="1">
+        <v>45922</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C49" s="1">
+        <v>45856</v>
+      </c>
+      <c r="D49" s="1">
+        <v>45923</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C50" s="1">
+        <v>45857</v>
+      </c>
+      <c r="D50" s="1">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C51" s="1">
+        <v>45858</v>
+      </c>
+      <c r="D51" s="1">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C52" s="1">
+        <v>45859</v>
+      </c>
+      <c r="D52" s="1">
+        <v>45926</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C53" s="1">
+        <v>45860</v>
+      </c>
+      <c r="D53" s="1">
+        <v>45927</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C54" s="1">
+        <v>45861</v>
+      </c>
+      <c r="D54" s="1">
+        <v>45928</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C55" s="1">
+        <v>45862</v>
+      </c>
+      <c r="D55" s="1">
+        <v>45929</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C56" s="1">
+        <v>45863</v>
+      </c>
+      <c r="D56" s="1">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C57" s="1">
+        <v>45864</v>
+      </c>
+      <c r="D57" s="1">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C58" s="1">
+        <v>45865</v>
+      </c>
+      <c r="D58" s="1">
+        <v>45932</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C59" s="1">
+        <v>45866</v>
+      </c>
+      <c r="D59" s="1">
+        <v>45933</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C60" s="1">
+        <v>45867</v>
+      </c>
+      <c r="D60" s="1">
+        <v>45934</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C61" s="1">
+        <v>45868</v>
+      </c>
+      <c r="D61" s="1">
+        <v>45935</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C62" s="1">
+        <v>45869</v>
+      </c>
+      <c r="D62" s="1">
+        <v>45936</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C63" s="1">
+        <v>45870</v>
+      </c>
+      <c r="D63" s="1">
+        <v>45937</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C64" s="1">
+        <v>45871</v>
+      </c>
+      <c r="D64" s="1">
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C65" s="1">
+        <v>45872</v>
+      </c>
+      <c r="D65" s="1">
+        <v>45939</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C66" s="1">
+        <v>45873</v>
+      </c>
+      <c r="D66" s="1">
+        <v>45940</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C67" s="1">
+        <v>45874</v>
+      </c>
+      <c r="D67" s="1">
+        <v>45941</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C68" s="1">
+        <v>45875</v>
+      </c>
+      <c r="D68" s="1">
+        <v>45942</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C69" s="1">
+        <v>45876</v>
+      </c>
+      <c r="D69" s="1">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C70" s="1">
+        <v>45877</v>
+      </c>
+      <c r="D70" s="1">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C71" s="1">
+        <v>45878</v>
+      </c>
+      <c r="D71" s="1">
+        <v>45945</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C72" s="1">
+        <v>45879</v>
+      </c>
+      <c r="D72" s="1">
+        <v>45946</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C73" s="1">
+        <v>45880</v>
+      </c>
+      <c r="D73" s="1">
+        <v>45947</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C74" s="1">
+        <v>45881</v>
+      </c>
+      <c r="D74" s="1">
+        <v>45948</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C75" s="1">
+        <v>45882</v>
+      </c>
+      <c r="D75" s="1">
+        <v>45949</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C76" s="1">
+        <v>45883</v>
+      </c>
+      <c r="D76" s="1">
+        <v>45950</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C77" s="1">
+        <v>45884</v>
+      </c>
+      <c r="D77" s="1">
+        <v>45951</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C78" s="1">
+        <v>45885</v>
+      </c>
+      <c r="D78" s="1">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C79" s="1">
+        <v>45886</v>
+      </c>
+      <c r="D79" s="1">
+        <v>45953</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C80" s="1">
+        <v>45887</v>
+      </c>
+      <c r="D80" s="1">
+        <v>45954</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C81" s="1">
+        <v>45888</v>
+      </c>
+      <c r="D81" s="1">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C82" s="1">
+        <v>45889</v>
+      </c>
+      <c r="D82" s="1">
+        <v>45956</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C83" s="1">
+        <v>45890</v>
+      </c>
+      <c r="D83" s="1">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C84" s="1">
+        <v>45891</v>
+      </c>
+      <c r="D84" s="1">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C85" s="1">
+        <v>45892</v>
+      </c>
+      <c r="D85" s="1">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C86" s="1">
+        <v>45893</v>
+      </c>
+      <c r="D86" s="1">
+        <v>45960</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C87" s="1">
+        <v>45894</v>
+      </c>
+      <c r="D87" s="1">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C88" s="1">
+        <v>45895</v>
+      </c>
+      <c r="D88" s="1">
+        <v>45962</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C89" s="1">
+        <v>45896</v>
+      </c>
+      <c r="D89" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C90" s="1">
+        <v>45897</v>
+      </c>
+      <c r="D90" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C91" s="1">
+        <v>45898</v>
+      </c>
+      <c r="D91" s="1">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C92" s="1">
+        <v>45899</v>
+      </c>
+      <c r="D92" s="1">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C93" s="1">
+        <v>45900</v>
+      </c>
+      <c r="D93" s="1">
+        <v>45967</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C94" s="1">
+        <v>45901</v>
+      </c>
+      <c r="D94" s="1">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C95" s="1">
+        <v>45902</v>
+      </c>
+      <c r="D95" s="1">
+        <v>45969</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C96" s="1">
+        <v>45903</v>
+      </c>
+      <c r="D96" s="1">
+        <v>45970</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C97" s="1">
+        <v>45904</v>
+      </c>
+      <c r="D97" s="1">
+        <v>45971</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C98" s="1">
+        <v>45905</v>
+      </c>
+      <c r="D98" s="1">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C99" s="1">
+        <v>45906</v>
+      </c>
+      <c r="D99" s="1">
+        <v>45973</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C100" s="1">
+        <v>45907</v>
+      </c>
+      <c r="D100" s="1">
+        <v>45974</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C101" s="1">
+        <v>45908</v>
+      </c>
+      <c r="D101" s="1">
+        <v>45975</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C102" s="1">
+        <v>45909</v>
+      </c>
+      <c r="D102" s="1">
+        <v>45976</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C103" s="1">
+        <v>45910</v>
+      </c>
+      <c r="D103" s="1">
+        <v>45977</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C104" s="1">
+        <v>45911</v>
+      </c>
+      <c r="D104" s="1">
+        <v>45978</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C105" s="1">
+        <v>45912</v>
+      </c>
+      <c r="D105" s="1">
+        <v>45979</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C106" s="1">
+        <v>45913</v>
+      </c>
+      <c r="D106" s="1">
+        <v>45980</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C107" s="1">
+        <v>45914</v>
+      </c>
+      <c r="D107" s="1">
+        <v>45981</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C108" s="1">
+        <v>45915</v>
+      </c>
+      <c r="D108" s="1">
+        <v>45982</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C109" s="1">
+        <v>45916</v>
+      </c>
+      <c r="D109" s="1">
+        <v>45983</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C110" s="1">
+        <v>45917</v>
+      </c>
+      <c r="D110" s="1">
+        <v>45984</v>
+      </c>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C111" s="1">
+        <v>45918</v>
+      </c>
+      <c r="D111" s="1">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C112" s="1">
+        <v>45919</v>
+      </c>
+      <c r="D112" s="1">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="113" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C113" s="1">
+        <v>45920</v>
+      </c>
+      <c r="D113" s="1">
+        <v>45987</v>
+      </c>
+    </row>
+    <row r="114" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C114" s="1">
+        <v>45921</v>
+      </c>
+      <c r="D114" s="1">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="115" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C115" s="1">
+        <v>45922</v>
+      </c>
+      <c r="D115" s="1">
+        <v>45989</v>
+      </c>
+    </row>
+    <row r="116" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C116" s="1">
+        <v>45923</v>
+      </c>
+      <c r="D116" s="1">
+        <v>45990</v>
+      </c>
+    </row>
+    <row r="117" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C117" s="1">
+        <v>45924</v>
+      </c>
+      <c r="D117" s="1">
+        <v>45991</v>
+      </c>
+    </row>
+    <row r="118" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C118" s="1">
+        <v>45925</v>
+      </c>
+      <c r="D118" s="1">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="119" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C119" s="1">
+        <v>45926</v>
+      </c>
+      <c r="D119" s="1">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="120" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C120" s="1">
+        <v>45927</v>
+      </c>
+      <c r="D120" s="1">
+        <v>45994</v>
+      </c>
+    </row>
+    <row r="121" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C121" s="1">
+        <v>45928</v>
+      </c>
+      <c r="D121" s="1">
+        <v>45995</v>
+      </c>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C122" s="1">
+        <v>45929</v>
+      </c>
+      <c r="D122" s="1">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C123" s="1">
+        <v>45930</v>
+      </c>
+      <c r="D123" s="1">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="124" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C124" s="1">
+        <v>45931</v>
+      </c>
+      <c r="D124" s="1">
+        <v>45998</v>
+      </c>
+    </row>
+    <row r="125" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C125" s="1">
+        <v>45932</v>
+      </c>
+      <c r="D125" s="1">
+        <v>45999</v>
+      </c>
+    </row>
+    <row r="126" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C126" s="1">
+        <v>45933</v>
+      </c>
+      <c r="D126" s="1">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="127" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C127" s="1">
+        <v>45934</v>
+      </c>
+      <c r="D127" s="1">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="128" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C128" s="1">
+        <v>45935</v>
+      </c>
+      <c r="D128" s="1">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="129" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C129" s="1">
+        <v>45936</v>
+      </c>
+      <c r="D129" s="1">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C130" s="1">
+        <v>45937</v>
+      </c>
+      <c r="D130" s="1">
+        <v>46004</v>
+      </c>
+    </row>
+    <row r="131" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C131" s="1">
+        <v>45938</v>
+      </c>
+      <c r="D131" s="1">
+        <v>46005</v>
+      </c>
+    </row>
+    <row r="132" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C132" s="1">
+        <v>45939</v>
+      </c>
+      <c r="D132" s="1">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="133" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C133" s="1">
+        <v>45940</v>
+      </c>
+      <c r="D133" s="1">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C134" s="1">
+        <v>45941</v>
+      </c>
+      <c r="D134" s="1">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="135" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C135" s="1">
+        <v>45942</v>
+      </c>
+      <c r="D135" s="1">
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="136" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C136" s="1">
+        <v>45943</v>
+      </c>
+      <c r="D136" s="1">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="137" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C137" s="1">
+        <v>45944</v>
+      </c>
+      <c r="D137" s="1">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="138" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C138" s="1">
+        <v>45945</v>
+      </c>
+      <c r="D138" s="1">
+        <v>46012</v>
+      </c>
+    </row>
+    <row r="139" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C139" s="1">
+        <v>45946</v>
+      </c>
+      <c r="D139" s="1">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="140" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C140" s="1">
+        <v>45947</v>
+      </c>
+      <c r="D140" s="1">
+        <v>46014</v>
+      </c>
+    </row>
+    <row r="141" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C141" s="1">
+        <v>45948</v>
+      </c>
+      <c r="D141" s="1">
+        <v>46015</v>
+      </c>
+    </row>
+    <row r="142" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C142" s="1">
+        <v>45949</v>
+      </c>
+      <c r="D142" s="1">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="143" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C143" s="1">
+        <v>45950</v>
+      </c>
+      <c r="D143" s="1">
+        <v>46017</v>
+      </c>
+    </row>
+    <row r="144" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C144" s="1">
+        <v>45951</v>
+      </c>
+      <c r="D144" s="1">
+        <v>46018</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C145" s="1">
+        <v>45952</v>
+      </c>
+      <c r="D145" s="1">
+        <v>46019</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C146" s="1">
+        <v>45953</v>
+      </c>
+      <c r="D146" s="1">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C147" s="1">
+        <v>45954</v>
+      </c>
+      <c r="D147" s="1">
+        <v>46021</v>
+      </c>
+    </row>
+    <row r="148" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C148" s="1">
+        <v>45955</v>
+      </c>
+      <c r="D148" s="1">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C149" s="1">
+        <v>45956</v>
+      </c>
+      <c r="D149" s="1">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C150" s="1">
+        <v>45957</v>
+      </c>
+      <c r="D150" s="1">
+        <v>46024</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C151" s="1">
+        <v>45958</v>
+      </c>
+      <c r="D151" s="1">
+        <v>46025</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C152" s="1">
+        <v>45959</v>
+      </c>
+      <c r="D152" s="1">
+        <v>46026</v>
+      </c>
+    </row>
+    <row r="153" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C153" s="1">
+        <v>45960</v>
+      </c>
+      <c r="D153" s="1">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="154" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C154" s="1">
+        <v>45961</v>
+      </c>
+      <c r="D154" s="1">
+        <v>46028</v>
+      </c>
+    </row>
+    <row r="155" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C155" s="1">
+        <v>45962</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="156" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C156" s="1">
+        <v>45963</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46030</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C157" s="1">
+        <v>45964</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C158" s="1">
+        <v>45965</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C159" s="1">
+        <v>45966</v>
+      </c>
+      <c r="D159" s="1">
+        <v>46033</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C160" s="1">
+        <v>45967</v>
+      </c>
+      <c r="D160" s="1">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="161" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C161" s="1">
+        <v>45968</v>
+      </c>
+      <c r="D161" s="1">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="162" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C162" s="1">
+        <v>45969</v>
+      </c>
+      <c r="D162" s="1">
+        <v>46036</v>
+      </c>
+    </row>
+    <row r="163" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C163" s="1">
+        <v>45970</v>
+      </c>
+      <c r="D163" s="1">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="164" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C164" s="1">
+        <v>45971</v>
+      </c>
+      <c r="D164" s="1">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="165" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C165" s="1">
+        <v>45972</v>
+      </c>
+      <c r="D165" s="1">
+        <v>46039</v>
+      </c>
+    </row>
+    <row r="166" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C166" s="1">
+        <v>45973</v>
+      </c>
+      <c r="D166" s="1">
+        <v>46040</v>
+      </c>
+    </row>
+    <row r="167" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C167" s="1">
+        <v>45974</v>
+      </c>
+      <c r="D167" s="1">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="168" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C168" s="1">
+        <v>45975</v>
+      </c>
+      <c r="D168" s="1">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="169" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C169" s="1">
+        <v>45976</v>
+      </c>
+      <c r="D169" s="1">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="170" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C170" s="1">
+        <v>45977</v>
+      </c>
+      <c r="D170" s="1">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="171" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C171" s="1">
+        <v>45978</v>
+      </c>
+      <c r="D171" s="1">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="172" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C172" s="1">
+        <v>45979</v>
+      </c>
+      <c r="D172" s="1">
+        <v>46046</v>
+      </c>
+    </row>
+    <row r="173" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C173" s="1">
+        <v>45980</v>
+      </c>
+      <c r="D173" s="1">
+        <v>46047</v>
+      </c>
+    </row>
+    <row r="174" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C174" s="1">
+        <v>45981</v>
+      </c>
+      <c r="D174" s="1">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="175" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C175" s="1">
+        <v>45982</v>
+      </c>
+      <c r="D175" s="1">
+        <v>46049</v>
+      </c>
+    </row>
+    <row r="176" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C176" s="1">
+        <v>45983</v>
+      </c>
+      <c r="D176" s="1">
+        <v>46050</v>
+      </c>
+    </row>
+    <row r="177" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C177" s="1">
+        <v>45984</v>
+      </c>
+      <c r="D177" s="1">
+        <v>46051</v>
+      </c>
+    </row>
+    <row r="178" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C178" s="1">
+        <v>45985</v>
+      </c>
+      <c r="D178" s="1">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="179" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C179" s="1">
+        <v>45986</v>
+      </c>
+      <c r="D179" s="1">
+        <v>46053</v>
+      </c>
+    </row>
+    <row r="180" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C180" s="1">
+        <v>45987</v>
+      </c>
+      <c r="D180" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="181" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C181" s="1">
+        <v>45988</v>
+      </c>
+      <c r="D181" s="1">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="182" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C182" s="1">
+        <v>45989</v>
+      </c>
+      <c r="D182" s="1">
+        <v>46056</v>
+      </c>
+    </row>
+    <row r="183" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C183" s="1">
+        <v>45990</v>
+      </c>
+      <c r="D183" s="1">
+        <v>46057</v>
+      </c>
+    </row>
+    <row r="184" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C184" s="1">
+        <v>45991</v>
+      </c>
+      <c r="D184" s="1">
+        <v>46058</v>
+      </c>
+    </row>
+    <row r="185" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C185" s="1">
+        <v>45992</v>
+      </c>
+      <c r="D185" s="1">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="186" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C186" s="1">
+        <v>45993</v>
+      </c>
+      <c r="D186" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="187" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C187" s="1">
+        <v>45994</v>
+      </c>
+      <c r="D187" s="1">
+        <v>46061</v>
+      </c>
+    </row>
+    <row r="188" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C188" s="1">
+        <v>45995</v>
+      </c>
+      <c r="D188" s="1">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="189" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C189" s="1">
+        <v>45996</v>
+      </c>
+      <c r="D189" s="1">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="190" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C190" s="1">
+        <v>45997</v>
+      </c>
+      <c r="D190" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="191" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C191" s="1">
+        <v>45998</v>
+      </c>
+      <c r="D191" s="1">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="192" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C192" s="1">
+        <v>45999</v>
+      </c>
+      <c r="D192" s="1">
+        <v>46066</v>
+      </c>
+    </row>
+    <row r="193" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C193" s="1">
+        <v>46000</v>
+      </c>
+      <c r="D193" s="1">
+        <v>46067</v>
+      </c>
+    </row>
+    <row r="194" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C194" s="1">
+        <v>46001</v>
+      </c>
+      <c r="D194" s="1">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="195" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C195" s="1">
+        <v>46002</v>
+      </c>
+      <c r="D195" s="1">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="196" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C196" s="1">
+        <v>46003</v>
+      </c>
+      <c r="D196" s="1">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="197" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C197" s="1">
+        <v>46004</v>
+      </c>
+      <c r="D197" s="1">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="198" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C198" s="1">
+        <v>46005</v>
+      </c>
+      <c r="D198" s="1">
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="199" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C199" s="1">
+        <v>46006</v>
+      </c>
+      <c r="D199" s="1">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="200" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C200" s="1">
+        <v>46007</v>
+      </c>
+      <c r="D200" s="1">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="201" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C201" s="1">
+        <v>46008</v>
+      </c>
+      <c r="D201" s="1">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="202" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C202" s="1">
+        <v>46009</v>
+      </c>
+      <c r="D202" s="1">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="203" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C203" s="1">
+        <v>46010</v>
+      </c>
+      <c r="D203" s="1">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="204" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C204" s="1">
+        <v>46011</v>
+      </c>
+      <c r="D204" s="1">
+        <v>46078</v>
+      </c>
+    </row>
+    <row r="205" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C205" s="1">
+        <v>46012</v>
+      </c>
+      <c r="D205" s="1">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="206" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C206" s="1">
+        <v>46013</v>
+      </c>
+      <c r="D206" s="1">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="207" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C207" s="1">
+        <v>46014</v>
+      </c>
+      <c r="D207" s="1">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="208" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C208" s="1">
+        <v>46015</v>
+      </c>
+      <c r="D208" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="209" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C209" s="1">
+        <v>46016</v>
+      </c>
+      <c r="D209" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="210" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C210" s="1">
+        <v>46017</v>
+      </c>
+      <c r="D210" s="1">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="211" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C211" s="1">
+        <v>46018</v>
+      </c>
+      <c r="D211" s="1">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="212" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C212" s="1">
+        <v>46019</v>
+      </c>
+      <c r="D212" s="1">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="213" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C213" s="1">
+        <v>46020</v>
+      </c>
+      <c r="D213" s="1">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="214" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C214" s="1">
+        <v>46021</v>
+      </c>
+      <c r="D214" s="1">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="215" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C215" s="1">
+        <v>46022</v>
+      </c>
+      <c r="D215" s="1">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="216" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C216" s="1">
+        <v>46023</v>
+      </c>
+      <c r="D216" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="217" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C217" s="1">
+        <v>46024</v>
+      </c>
+      <c r="D217" s="1">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="218" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C218" s="1">
+        <v>46025</v>
+      </c>
+      <c r="D218" s="1">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="219" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C219" s="1">
+        <v>46026</v>
+      </c>
+      <c r="D219" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="220" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C220" s="1">
+        <v>46027</v>
+      </c>
+      <c r="D220" s="1">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="221" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C221" s="1">
+        <v>46028</v>
+      </c>
+      <c r="D221" s="1">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="222" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C222" s="1">
+        <v>46029</v>
+      </c>
+      <c r="D222" s="1">
+        <v>46096</v>
+      </c>
+    </row>
+    <row r="223" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C223" s="1">
+        <v>46030</v>
+      </c>
+      <c r="D223" s="1">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="224" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C224" s="1">
+        <v>46031</v>
+      </c>
+      <c r="D224" s="1">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="225" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C225" s="1">
+        <v>46032</v>
+      </c>
+      <c r="D225" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="226" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C226" s="1">
+        <v>46033</v>
+      </c>
+      <c r="D226" s="1">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="227" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C227" s="1">
+        <v>46034</v>
+      </c>
+      <c r="D227" s="1">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="228" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C228" s="1">
+        <v>46035</v>
+      </c>
+      <c r="D228" s="1">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="229" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C229" s="1">
+        <v>46036</v>
+      </c>
+      <c r="D229" s="1">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="230" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C230" s="1">
+        <v>46037</v>
+      </c>
+      <c r="D230" s="1">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="231" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C231" s="1">
+        <v>46038</v>
+      </c>
+      <c r="D231" s="1">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="232" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C232" s="1">
+        <v>46039</v>
+      </c>
+      <c r="D232" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="233" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C233" s="1">
+        <v>46040</v>
+      </c>
+      <c r="D233" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="234" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C234" s="1">
+        <v>46041</v>
+      </c>
+      <c r="D234" s="1">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="235" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C235" s="1">
+        <v>46042</v>
+      </c>
+      <c r="D235" s="1">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="236" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C236" s="1">
+        <v>46043</v>
+      </c>
+      <c r="D236" s="1">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="237" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C237" s="1">
+        <v>46044</v>
+      </c>
+      <c r="D237" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="238" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C238" s="1">
+        <v>46045</v>
+      </c>
+      <c r="D238" s="1">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="239" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C239" s="1">
+        <v>46046</v>
+      </c>
+      <c r="D239" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="240" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C240" s="1">
+        <v>46047</v>
+      </c>
+      <c r="D240" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="241" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C241" s="1">
+        <v>46048</v>
+      </c>
+      <c r="D241" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="242" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C242" s="1">
+        <v>46049</v>
+      </c>
+      <c r="D242" s="1">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="243" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C243" s="1">
+        <v>46050</v>
+      </c>
+      <c r="D243" s="1">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="244" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C244" s="1">
+        <v>46051</v>
+      </c>
+      <c r="D244" s="1">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="245" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C245" s="1">
+        <v>46052</v>
+      </c>
+      <c r="D245" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="246" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C246" s="1">
+        <v>46053</v>
+      </c>
+      <c r="D246" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="247" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C247" s="1">
+        <v>46054</v>
+      </c>
+      <c r="D247" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="248" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C248" s="1">
+        <v>46055</v>
+      </c>
+      <c r="D248" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="249" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C249" s="1">
+        <v>46056</v>
+      </c>
+      <c r="D249" s="1">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="250" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C250" s="1">
+        <v>46057</v>
+      </c>
+      <c r="D250" s="1">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="251" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C251" s="1">
+        <v>46058</v>
+      </c>
+      <c r="D251" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="252" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C252" s="1">
+        <v>46059</v>
+      </c>
+      <c r="D252" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="253" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C253" s="1">
+        <v>46060</v>
+      </c>
+      <c r="D253" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="254" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C254" s="1">
+        <v>46061</v>
+      </c>
+      <c r="D254" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="255" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C255" s="1">
+        <v>46062</v>
+      </c>
+      <c r="D255" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="256" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C256" s="1">
+        <v>46063</v>
+      </c>
+      <c r="D256" s="1">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="257" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C257" s="1">
+        <v>46064</v>
+      </c>
+      <c r="D257" s="1">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="258" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C258" s="1">
+        <v>46065</v>
+      </c>
+      <c r="D258" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="259" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C259" s="1">
+        <v>46066</v>
+      </c>
+      <c r="D259" s="1">
+        <v>46133</v>
       </c>
     </row>
   </sheetData>
@@ -1190,6 +3081,89 @@
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA768B00-7436-476F-8313-3EEB8BEE37F9}">
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCA75C8-D14E-438D-8BA1-C1CE920F777B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56151ED7-57F4-4FF9-8834-4B04C53676AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="11" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="154">
   <si>
     <t>UserName</t>
   </si>
@@ -440,6 +440,75 @@
   </si>
   <si>
     <t>Pending/Sent for Generator Signature</t>
+  </si>
+  <si>
+    <t>1 - Clean Earth of Calvert City (AESKY)</t>
+  </si>
+  <si>
+    <t>2 - Clean Earth of Morgantown (AESWV)</t>
+  </si>
+  <si>
+    <t>257 - Republic Env Sys  (PA) LLC</t>
+  </si>
+  <si>
+    <t>3 - Clean Earth of North Jersey, Inc. (CENJ)</t>
+  </si>
+  <si>
+    <t>547 - Clean Earth of Maryland, Inc. (CEM)</t>
+  </si>
+  <si>
+    <t>946 - Allworth, Inc. (ESOL)</t>
+  </si>
+  <si>
+    <t>2138 - Petro-Chem Processing Group (ESOL)</t>
+  </si>
+  <si>
+    <t>2648 - Clean Earth of New Castle (CENC)</t>
+  </si>
+  <si>
+    <t>DropdownValues</t>
+  </si>
+  <si>
+    <t>Container #</t>
+  </si>
+  <si>
+    <t>Container # Range ( n - m )</t>
+  </si>
+  <si>
+    <t>Inbound Manifest Tracking #</t>
+  </si>
+  <si>
+    <t>Outbound Manifest Tracking #</t>
+  </si>
+  <si>
+    <t>Inbound Workorder #</t>
+  </si>
+  <si>
+    <t>Outbound Workorder #</t>
+  </si>
+  <si>
+    <t>Profile # (Exact)</t>
+  </si>
+  <si>
+    <t>Profile # (Like)</t>
+  </si>
+  <si>
+    <t>Profile Description</t>
+  </si>
+  <si>
+    <t>Generator</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>AES Code</t>
+  </si>
+  <si>
+    <t>Offspec Code</t>
+  </si>
+  <si>
+    <t>EPA Code</t>
   </si>
 </sst>
 </file>
@@ -854,7 +923,7 @@
         <v>45809</v>
       </c>
       <c r="D2" s="1">
-        <v>45876</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -3090,80 +3159,128 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA768B00-7436-476F-8313-3EEB8BEE37F9}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B1" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3574,7 +3691,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04396675-12D6-4914-9522-1C9ED27AC3F7}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" customWidth="1"/>
@@ -3613,6 +3730,46 @@
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56151ED7-57F4-4FF9-8834-4B04C53676AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4D0D83-3DF6-4A9E-92DD-3E064169C592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="156">
   <si>
     <t>UserName</t>
   </si>
@@ -509,6 +509,12 @@
   </si>
   <si>
     <t>EPA Code</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
   </si>
 </sst>
 </file>
@@ -550,11 +556,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1681,16 +1688,16 @@
       </c>
     </row>
     <row r="95" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C95" s="1">
-        <v>45902</v>
+      <c r="C95" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="D95" s="1">
         <v>45969</v>
       </c>
     </row>
     <row r="96" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C96" s="1">
-        <v>45903</v>
+      <c r="C96" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="D96" s="1">
         <v>45970</v>
@@ -3840,7 +3847,7 @@
         <v>50</v>
       </c>
       <c r="D4">
-        <v>87058</v>
+        <v>87064</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F4D0D83-3DF6-4A9E-92DD-3E064169C592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D723DE9C-41F7-4395-9D24-7339000242F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="9" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="173">
   <si>
     <t>UserName</t>
   </si>
@@ -515,6 +515,57 @@
   </si>
   <si>
     <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>ZZ7700</t>
+  </si>
+  <si>
+    <t>ZZ3500</t>
+  </si>
+  <si>
+    <t>ZZ3200</t>
+  </si>
+  <si>
+    <t>ZZ7300</t>
+  </si>
+  <si>
+    <t>ZZ7400</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 - Ross Incineration Services, Inc. - 36790 </t>
+  </si>
+  <si>
+    <t>139982 (ROSS) PERACETIC ACID SOLUTION</t>
+  </si>
+  <si>
+    <t>UN3107, Organic peroxide type E, liquid, 5.2</t>
+  </si>
+  <si>
+    <t>140390 (ROSS) CHLOROCRESOL</t>
+  </si>
+  <si>
+    <t>UN2811, Toxic solids, organic, n.o.s., 6.1, PG-II</t>
+  </si>
+  <si>
+    <t>149538ROSS (ROSS) SODIUM METHOXIDE &amp; METHANOL</t>
+  </si>
+  <si>
+    <t>UN1289, Sodium methylate solutions [in alcohol], 3 (8), PG-III</t>
+  </si>
+  <si>
+    <t>23847ROSS (ROSS) NON-RCRA ISOCYANATES</t>
+  </si>
+  <si>
+    <t>Non-RCRA, Non-DOT Regulated Material</t>
+  </si>
+  <si>
+    <t>25347 (ROSS) SPECIMENTS IN FORMALIN - NON RCRA</t>
+  </si>
+  <si>
+    <t>UN2209, Formaldehyde, solutions, [with not less than 25 percent formaldehyde], 8, PG-III</t>
   </si>
 </sst>
 </file>
@@ -906,16 +957,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -976,6 +1027,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
       <c r="C6" s="1">
         <v>45813</v>
       </c>
@@ -3014,7 +3071,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67A0C787-9629-4F1D-ABA0-794DC4D85B37}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="63.90625" customWidth="1"/>
@@ -3067,6 +3124,46 @@
       </c>
       <c r="B6" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3617,7 +3714,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8441AC03-8AA1-4A52-B022-D9D96F5EE941}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.81640625" customWidth="1"/>
@@ -3651,6 +3748,31 @@
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>25708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3698,7 +3820,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04396675-12D6-4914-9522-1C9ED27AC3F7}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" customWidth="1"/>
@@ -3777,6 +3899,11 @@
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D723DE9C-41F7-4395-9D24-7339000242F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A024416B-47D6-4A65-A5A3-96D30F637BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="9" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="12" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="ManifestProfiles" sheetId="7" r:id="rId10"/>
     <sheet name="Container" sheetId="10" r:id="rId11"/>
     <sheet name="Values" sheetId="12" r:id="rId12"/>
+    <sheet name="Countries" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="198">
   <si>
     <t>UserName</t>
   </si>
@@ -566,6 +568,81 @@
   </si>
   <si>
     <t>UN2209, Formaldehyde, solutions, [with not less than 25 percent formaldehyde], 8, PG-III</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MD</t>
   </si>
 </sst>
 </file>
@@ -3392,6 +3469,137 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09680BFD-9157-468B-A772-E5A0926A98E5}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF68588-F67D-4E6D-B0F8-A93ADDD87F15}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97C34AAF-0049-4621-ACC0-F8AB61C4FEAD}">
   <dimension ref="A1:B4"/>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A024416B-47D6-4A65-A5A3-96D30F637BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7294AB-A4A0-4FE5-B5C5-C0C35677412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="12" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="12" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="220">
   <si>
     <t>UserName</t>
   </si>
@@ -643,6 +643,72 @@
   </si>
   <si>
     <t>MD</t>
+  </si>
+  <si>
+    <t>County</t>
+  </si>
+  <si>
+    <t>Aleutians East</t>
+  </si>
+  <si>
+    <t>Aleutians West</t>
+  </si>
+  <si>
+    <t>Anchorage</t>
+  </si>
+  <si>
+    <t>Bethel</t>
+  </si>
+  <si>
+    <t>Bristol Bay</t>
+  </si>
+  <si>
+    <t>Denali</t>
+  </si>
+  <si>
+    <t>Dillingham</t>
+  </si>
+  <si>
+    <t>Fairbanks North Star</t>
+  </si>
+  <si>
+    <t>Haines</t>
+  </si>
+  <si>
+    <t>Juneau</t>
+  </si>
+  <si>
+    <t>Kenai Peninsula</t>
+  </si>
+  <si>
+    <t>Ketchikan Gateway</t>
+  </si>
+  <si>
+    <t>Kodiak Island</t>
+  </si>
+  <si>
+    <t>Lake and Peninsula</t>
+  </si>
+  <si>
+    <t>Appling</t>
+  </si>
+  <si>
+    <t>State-Georgia</t>
+  </si>
+  <si>
+    <t>Atkinson</t>
+  </si>
+  <si>
+    <t>Bacon</t>
+  </si>
+  <si>
+    <t>Baker</t>
+  </si>
+  <si>
+    <t>Baldwin</t>
+  </si>
+  <si>
+    <t>Barrow</t>
   </si>
 </sst>
 </file>
@@ -3471,119 +3537,196 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09680BFD-9157-468B-A772-E5A0926A98E5}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.26953125" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>174</v>
       </c>
       <c r="B2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>175</v>
       </c>
       <c r="B3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>176</v>
       </c>
       <c r="B4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>177</v>
       </c>
       <c r="B5" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>178</v>
       </c>
       <c r="B6" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C6" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>179</v>
       </c>
       <c r="B7" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>180</v>
       </c>
       <c r="B8" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C10" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>197</v>
+      </c>
+      <c r="C17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C18" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A7294AB-A4A0-4FE5-B5C5-C0C35677412B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1B79DA-63D7-42D2-BC2D-A889D84542A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="12" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="7" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="221">
   <si>
     <t>UserName</t>
   </si>
@@ -709,19 +709,28 @@
   </si>
   <si>
     <t>Barrow</t>
+  </si>
+  <si>
+    <t>2079 - Clean Earth of Alabama, Inc. (CEA)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -750,12 +759,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3214,7 +3224,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67A0C787-9629-4F1D-ABA0-794DC4D85B37}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="63.90625" customWidth="1"/>
@@ -3307,6 +3317,11 @@
       </c>
       <c r="B11" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>2500024674</v>
       </c>
     </row>
   </sheetData>
@@ -4133,7 +4148,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91236A0F-D4E4-4590-95E3-BE447AD5E61E}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" customWidth="1"/>
@@ -4164,6 +4179,11 @@
         <v>108</v>
       </c>
     </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4171,7 +4191,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04396675-12D6-4914-9522-1C9ED27AC3F7}">
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" customWidth="1"/>
@@ -4255,6 +4275,11 @@
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Test Data.xlsx
+++ b/testdata/Test Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kshyamsai\eclipse-workspace\Testconnectplus11032022\CorePlayWrightAutomationFramework\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1B79DA-63D7-42D2-BC2D-A889D84542A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6451DDA3-F2B1-4DF1-B176-06BB8B5BFF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="7" xr2:uid="{6C5D5E3E-38B6-4BB9-8E1D-73DE712EDA8B}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="222">
   <si>
     <t>UserName</t>
   </si>
@@ -712,6 +712,9 @@
   </si>
   <si>
     <t>2079 - Clean Earth of Alabama, Inc. (CEA)</t>
+  </si>
+  <si>
+    <t>3308 - Chemical Reclamation Services</t>
   </si>
 </sst>
 </file>
@@ -4191,7 +4194,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04396675-12D6-4914-9522-1C9ED27AC3F7}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="91.81640625" customWidth="1"/>
@@ -4280,6 +4283,11 @@
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>220</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
